--- a/src/attributions/attributions_ig_traj_475.xlsx
+++ b/src/attributions/attributions_ig_traj_475.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG6"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,25 +999,25 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.4505058523318891</v>
+        <v>-0.5117690562124095</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.244351309497955</v>
+        <v>0.4195157542055902</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.001294996927079795</v>
+        <v>-0.004314055241844765</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1026,25 +1026,25 @@
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.07624818188297519</v>
+        <v>-0.125017873923628</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1819651761675748</v>
+        <v>0.3538704663450428</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02047403154812535</v>
+        <v>0.01927852208603374</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
@@ -1053,103 +1053,103 @@
         <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.179202534595245</v>
+        <v>-0.1668902047734336</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0005226644428547175</v>
+        <v>0.08437635980091775</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.01142098779942313</v>
+        <v>0.03719702359491332</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1539734489233655</v>
+        <v>0.1046105516957544</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.1222015625552669</v>
+        <v>0.3577766543431803</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.007973130565890371</v>
+        <v>-0.1835203905499175</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>-0</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.07260216844690356</v>
+        <v>-0.2904231897738008</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.05311191977630729</v>
+        <v>0.123329808062515</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.06263930157042599</v>
+        <v>-0.4117364358618215</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.3800041985145637</v>
+        <v>-0.5399046857060006</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.08924683921157603</v>
+        <v>0.6116223830084256</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.09779416912466242</v>
+        <v>0.09489561560165498</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0</v>
@@ -1158,25 +1158,25 @@
         <v>-0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1502308647047033</v>
+        <v>0.07807609226691654</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1534836506933853</v>
+        <v>0.01396280076124668</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.1009778184498374</v>
+        <v>0.04866314201619848</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
@@ -1185,25 +1185,25 @@
         <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL2" t="n">
         <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.02276615780905083</v>
+        <v>0.2133057873074318</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.07647982753982757</v>
+        <v>0.07579026270364853</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.1632327355909123</v>
+        <v>0.02572567469716819</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR2" t="n">
         <v>-0</v>
@@ -1218,19 +1218,19 @@
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.09750225753647181</v>
+        <v>-0.2306099805982746</v>
       </c>
       <c r="BW2" t="n">
         <v>-0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.03115148144972534</v>
+        <v>0.2218222183461628</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.04912258871906942</v>
+        <v>0.003152169451063791</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
@@ -1245,22 +1245,22 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.1575308841891037</v>
+        <v>0.3455943078386516</v>
       </c>
       <c r="CF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.07316674924220792</v>
+        <v>-0.2783236008757467</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.02947392017259585</v>
+        <v>0.1007847006780193</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK2" t="n">
         <v>-0</v>
@@ -1272,49 +1272,49 @@
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.008928231515021465</v>
+        <v>0.2815810864352452</v>
       </c>
       <c r="CO2" t="n">
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.06310445774046425</v>
+        <v>-0.5355701039058656</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.11302350949324</v>
+        <v>0.02016205026974819</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV2" t="n">
         <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.1724305960011671</v>
+        <v>0.3565372978912811</v>
       </c>
       <c r="CX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.08133339044781608</v>
+        <v>-0.3084776323621077</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.02974248277682708</v>
+        <v>0.05249567383816202</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
@@ -1326,16 +1326,16 @@
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.08485804074362797</v>
+        <v>0.08618963480545379</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.1207334179223142</v>
+        <v>-0.1940433518111573</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.02086867508135017</v>
+        <v>0.0138152685124003</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
@@ -1347,112 +1347,112 @@
         <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.05551839592985888</v>
+        <v>0.1261671835750078</v>
       </c>
       <c r="DP2" t="n">
         <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.004058009809756709</v>
+        <v>-0.1919736492891344</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.08709067232396704</v>
+        <v>-0.06095682592883223</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV2" t="n">
         <v>-0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1801956190367895</v>
+        <v>-0.1282273591766326</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.1070999758365286</v>
+        <v>0.09645245757228139</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.02782153105994483</v>
+        <v>0.09859677653944274</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF2" t="n">
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.100830613843518</v>
+        <v>0.3229321989547703</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.03296826173760557</v>
+        <v>-0.2640738200418214</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.09529988177614328</v>
+        <v>0.01980752411249512</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.08667155746405804</v>
+        <v>0.2776918706694398</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.05554544277582604</v>
+        <v>-0.1305530964411894</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.01565767147851718</v>
+        <v>0.05882275741894463</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.170625078530698</v>
+        <v>0.3936173961915459</v>
       </c>
       <c r="EZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.06963877469135504</v>
+        <v>-0.3627704521888376</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.03737224599198746</v>
+        <v>0.09396005879444098</v>
       </c>
       <c r="FC2" t="n">
         <v>0</v>
       </c>
       <c r="FD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE2" t="n">
         <v>-0</v>
@@ -1488,46 +1488,46 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.03933326812522981</v>
+        <v>0.1761670705129588</v>
       </c>
       <c r="FI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.02352417217950863</v>
+        <v>-0.1555925843776071</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.0857711925031354</v>
+        <v>0.1408742659104169</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.1140771090576381</v>
+        <v>0.4176620298394561</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.06705042446545584</v>
+        <v>-0.442318434835894</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.05099820025138803</v>
+        <v>-0.456227389700363</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
@@ -1539,31 +1539,31 @@
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.07441780321743119</v>
+        <v>0.3215379853961916</v>
       </c>
       <c r="GA2" t="n">
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.06088306690605251</v>
+        <v>-0.2735162900055763</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="3">
@@ -2137,100 +2137,100 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03062115259976216</v>
+        <v>-0.1693732619885591</v>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1955275815922316</v>
+        <v>0.06079141769187531</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.17257151035322</v>
+        <v>0.005505188060195435</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.04802955157209386</v>
+        <v>-0.1413732939277481</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.05651373471752422</v>
+        <v>0.02681534176380763</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02108756773478567</v>
+        <v>-0.06504555462954867</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0236807673043541</v>
+        <v>0.006954748461946557</v>
       </c>
       <c r="T4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1992897559679832</v>
+        <v>0.07320374439702694</v>
       </c>
       <c r="V4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1133754542403832</v>
+        <v>-0.05783702132455627</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.05165228433792743</v>
+        <v>0.05899728363163514</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0.06932481460038355</v>
+        <v>-0.06823502607507552</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1068949030927628</v>
+        <v>-0.09530145402991766</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -2242,55 +2242,55 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-0.02718765331017629</v>
+        <v>-0.02221195573001947</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.08052461714031939</v>
+        <v>-0.05544453856437018</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.07586887946175391</v>
+        <v>-0.07719319433879077</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.0657902511226558</v>
+        <v>-0.1184046003802212</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0.3709723778767429</v>
+        <v>0.03703783963456602</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.6440694554035398</v>
+        <v>-0.2207800481383475</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
         <v>0</v>
@@ -2299,19 +2299,19 @@
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1912558998056247</v>
+        <v>-0.02170443802265675</v>
       </c>
       <c r="BD4" t="n">
         <v>-0</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.08217544607357781</v>
+        <v>0.0261811848060196</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.03374417725315601</v>
+        <v>0.2226673793662126</v>
       </c>
       <c r="BH4" t="n">
         <v>-0</v>
@@ -2323,103 +2323,103 @@
         <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.05657804708269079</v>
+        <v>0.1383800126709225</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0.2707584385663753</v>
+        <v>0.03396756115751867</v>
       </c>
       <c r="BO4" t="n">
         <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.1841849246213437</v>
+        <v>-0.0120228719260994</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.01571373288459509</v>
+        <v>-0.1045865638606037</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>-0.04205322991055547</v>
+        <v>0.08090713619105019</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.1632287545994114</v>
+        <v>-0.0798946369882212</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.004848191350634763</v>
+        <v>0.08827532453689216</v>
       </c>
       <c r="CE4" t="n">
         <v>0</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.06841239082562438</v>
+        <v>-0.001513579057020402</v>
       </c>
       <c r="CG4" t="n">
         <v>0</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.08186494693737588</v>
+        <v>0.03919862071565339</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0004278899115772833</v>
+        <v>-0.0199850229403016</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0.0119785081708646</v>
+        <v>-0.06209801518148265</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.3339617115841477</v>
+        <v>-0.05701341090051124</v>
       </c>
       <c r="CR4" t="n">
         <v>-0</v>
@@ -2428,79 +2428,79 @@
         <v>-0</v>
       </c>
       <c r="CT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU4" t="n">
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.02115484154118716</v>
+        <v>0.07611283190744425</v>
       </c>
       <c r="CW4" t="n">
         <v>-0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0372156767764293</v>
+        <v>-0.01489282244718633</v>
       </c>
       <c r="CY4" t="n">
         <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.02082340058021804</v>
+        <v>0.002156278356693555</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0.02700404164792446</v>
+        <v>0.01701420403030056</v>
       </c>
       <c r="DF4" t="n">
         <v>0</v>
       </c>
       <c r="DG4" t="n">
-        <v>-0.00368079002895792</v>
+        <v>6.764998842408459e-05</v>
       </c>
       <c r="DH4" t="n">
         <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.1901009925726771</v>
+        <v>0.1140059510592098</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.2033633889026844</v>
+        <v>0.09886822328868039</v>
       </c>
       <c r="DO4" t="n">
         <v>0</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.05319271762902555</v>
+        <v>0.04437650728799912</v>
       </c>
       <c r="DQ4" t="n">
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.04835993313168636</v>
+        <v>-0.03331752149057207</v>
       </c>
       <c r="DS4" t="n">
         <v>-0</v>
@@ -2509,25 +2509,25 @@
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>-0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.1057286255996383</v>
+        <v>0.01255783918561747</v>
       </c>
       <c r="DX4" t="n">
         <v>0</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.08692639358441072</v>
+        <v>0.1598382681277296</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.05785648057336356</v>
+        <v>-0.06356206433311165</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
@@ -2542,46 +2542,46 @@
         <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.07722077766713316</v>
+        <v>0.04475559286813059</v>
       </c>
       <c r="EG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.1209126236727128</v>
+        <v>0.03329761082541826</v>
       </c>
       <c r="EI4" t="n">
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.04796779558064184</v>
+        <v>0.06553280941369871</v>
       </c>
       <c r="EK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM4" t="n">
         <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.1133141525290822</v>
+        <v>0.0374454701175622</v>
       </c>
       <c r="EP4" t="n">
         <v>0</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.04480506257121101</v>
+        <v>-0.007114749185716409</v>
       </c>
       <c r="ER4" t="n">
         <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.1952866539230739</v>
+        <v>0.07188969922290318</v>
       </c>
       <c r="ET4" t="n">
         <v>0</v>
@@ -2596,52 +2596,52 @@
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.03346275455074199</v>
+        <v>0.07594896548536706</v>
       </c>
       <c r="EY4" t="n">
         <v>0</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.04402736527221673</v>
+        <v>-0.02934872653171687</v>
       </c>
       <c r="FA4" t="n">
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.02623116368395766</v>
+        <v>0.02510918958867662</v>
       </c>
       <c r="FC4" t="n">
         <v>0</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>-0.001807630908447534</v>
+        <v>0.2482907545379775</v>
       </c>
       <c r="FH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0150046206251732</v>
+        <v>0.067857084446046</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.09898439076842994</v>
+        <v>-0.09202466178025805</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
@@ -2650,46 +2650,46 @@
         <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>-0.00906283408862534</v>
+        <v>0.1585275340015465</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.001547035093802839</v>
+        <v>0.001809725062176173</v>
       </c>
       <c r="FS4" t="n">
         <v>0</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.006039508556990533</v>
+        <v>5.461173387764513e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.03039259621017778</v>
+        <v>0.1327394196892093</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0.04720092184352599</v>
+        <v>-0.011154831937886</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
         <v>0</v>
@@ -2701,24 +2701,24 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.238456692718633</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.1239170049396501</v>
+        <v>0.6717412644198602</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>-0.3459774649901818</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.07258444784265004</v>
+        <v>-0.1408458591164069</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2727,25 +2727,25 @@
         <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2741820163335187</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.06822463842497406</v>
+        <v>0.5111789318449366</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>-0.3980178850330766</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01074076574964042</v>
+        <v>-0.1156010431512941</v>
       </c>
       <c r="O5" t="n">
         <v>-0</v>
@@ -2760,46 +2760,46 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01559377993059474</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1151609680749472</v>
+        <v>0.1150757055029075</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1049270538201726</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0002185099850411126</v>
+        <v>-0.05502361335119652</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.03776068233084083</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1230672581492239</v>
+        <v>0.04079986244182714</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-0.1386122322738988</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.0261862085345809</v>
+        <v>0.01586888723390617</v>
       </c>
       <c r="AG5" t="n">
         <v>-0</v>
@@ -2808,31 +2808,31 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02940958488101629</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.01087160352067526</v>
+        <v>0.3686315292382823</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-0.1296466012062424</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.01099073724392375</v>
+        <v>0.2887664420174652</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
@@ -2841,127 +2841,127 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.06254241697238057</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.1411503162645911</v>
+        <v>0.7456032977266327</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0.2590724333074738</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.2062754360066463</v>
+        <v>-0.2506406010791589</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.120959769754411</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01685496429886224</v>
+        <v>-0.08408203607066513</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>-0.1106133240858495</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1009471743947578</v>
+        <v>-0.1903013537104588</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.00673890519904214</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.07641641262521175</v>
+        <v>-0.1262421716686517</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0.005033421918449282</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.1237331144092931</v>
+        <v>0.06161154342284621</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0009198392037120118</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.1124103121865303</v>
+        <v>0.2736356277089824</v>
       </c>
       <c r="BW5" t="n">
         <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>-0.1375021528260741</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.1010656252699253</v>
+        <v>-0.02541873058455054</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.02986108933299455</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.02981860686252328</v>
+        <v>-0.3499757544405464</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>0.2110198083748915</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01751060621524351</v>
+        <v>-0.0005544144532974372</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2970,25 +2970,25 @@
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.04579319710014999</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.01122721754271804</v>
+        <v>-0.3319920903018774</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0</v>
+        <v>0.2696676894262885</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.04045168308433263</v>
+        <v>0.1060851944819201</v>
       </c>
       <c r="CR5" t="n">
         <v>-0</v>
@@ -3003,73 +3003,73 @@
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.01577666574735011</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.03666983972159344</v>
+        <v>-0.3445087658722512</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0</v>
+        <v>0.2199692333061976</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01606321094270193</v>
+        <v>0.02586640851552291</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.03569055311171988</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.08594772025990499</v>
+        <v>-0.1436670654253945</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>-0.01343143831961954</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.02103898790905519</v>
+        <v>0.002761875403543211</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.004810917776666982</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0471800280732062</v>
+        <v>-0.171321903194157</v>
       </c>
       <c r="DP5" t="n">
         <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>0.09405566137547063</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.03214099613749245</v>
+        <v>-0.07810496863575508</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -3081,163 +3081,163 @@
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.02629846220721314</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.108275642338052</v>
+        <v>0.1111487250487953</v>
       </c>
       <c r="DY5" t="n">
         <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0</v>
+        <v>0.1191454376358886</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.06625005364730968</v>
+        <v>0.07863897353638541</v>
       </c>
       <c r="EB5" t="n">
         <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.02434662461221672</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.03037555766926546</v>
+        <v>-0.3006526229909773</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>0.1579350260194744</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.01344040023762003</v>
+        <v>0.07427731333657024</v>
       </c>
       <c r="EK5" t="n">
         <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.01960577694563968</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0267513727478193</v>
+        <v>-0.219683697522238</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>-0.1056384232965031</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.07792353491952389</v>
+        <v>0.03611325962762819</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.02022123578310596</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.03484850182794873</v>
+        <v>-0.394961491465901</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>0.245928669353869</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.041388902913031</v>
+        <v>0.005183576098906574</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.01134374694771397</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01432189747644374</v>
+        <v>-0.1887507634191651</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>0.1438525842650411</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0950041504360204</v>
+        <v>0.0382914108756744</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
         <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>-0.03529597212202507</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.1291774338078065</v>
+        <v>0.02683811728291709</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>0.2689426258937449</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.1687695711088741</v>
+        <v>-0.001116192321405666</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
@@ -3246,28 +3246,28 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.05586756045222661</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.004333027859342422</v>
+        <v>-0.3004631713520333</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>0.1366780990875608</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.5371093824933619</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0</v>
+        <v>0.0578156940072551</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.2992572350043922</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.4690752752099394</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,25 +3314,25 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0</v>
+        <v>-0.06603715374026575</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.1404309447915725</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.1326222977249406</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,16 +3341,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0</v>
+        <v>-0.137523951086214</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.00279198292134876</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.02162734999673137</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -3368,16 +3368,16 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0</v>
+        <v>-0.2968039009603459</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0.07271744441825191</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>0.1640999256283156</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,16 +3395,16 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0</v>
+        <v>0.06105524146132357</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>-0.06899437717374408</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>0.5503978606696078</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3422,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0</v>
+        <v>-0.2409741280655246</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>-0.2007222559845896</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>0.1431926460566251</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,16 +3449,16 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0</v>
+        <v>-0.06979663346539815</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>-0.225971117739555</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,19 +3467,19 @@
         <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>-0.03179768655582656</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
         <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0</v>
+        <v>0.0918501273292391</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>0.03489558862093572</v>
       </c>
       <c r="BR6" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>0.2004856328162341</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,37 +3503,37 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0</v>
+        <v>0.0006670003333749474</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>-0.05214243798388071</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>0</v>
+        <v>-0.203988040595648</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0</v>
+        <v>-0.06908967381596247</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>0.1489696140742285</v>
       </c>
       <c r="CJ6" t="n">
         <v>0</v>
@@ -3548,34 +3548,34 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0</v>
+        <v>-0.2281556930765397</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0</v>
+        <v>0.1007837645045368</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>0.1179214605723272</v>
       </c>
       <c r="CS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT6" t="n">
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0</v>
+        <v>-0.1916915819249067</v>
       </c>
       <c r="CX6" t="n">
         <v>0</v>
@@ -3584,25 +3584,25 @@
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0</v>
+        <v>-0.05824291778663477</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>0.1507184428673861</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>0</v>
+        <v>-0.1111978687539998</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
@@ -3611,10 +3611,10 @@
         <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0</v>
+        <v>-0.1772974592938191</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>0.03868343354232751</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,109 +3623,109 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0</v>
+        <v>-0.1052754056299559</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
         <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0</v>
+        <v>-0.03323889399680438</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>0.1453473111287974</v>
       </c>
       <c r="DT6" t="n">
         <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0</v>
+        <v>-0.01004295350398735</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0</v>
+        <v>0.1331052283795266</v>
       </c>
       <c r="EB6" t="n">
-        <v>0</v>
+        <v>0.1097716377820041</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
         <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0</v>
+        <v>-0.09297901498361785</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0</v>
+        <v>-0.08876371378672587</v>
       </c>
       <c r="EK6" t="n">
-        <v>0</v>
+        <v>0.05829340368553564</v>
       </c>
       <c r="EL6" t="n">
         <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0</v>
+        <v>-0.0866179313832318</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0</v>
+        <v>-0.1469840428171998</v>
       </c>
       <c r="ET6" t="n">
-        <v>0</v>
+        <v>0.1970082558287144</v>
       </c>
       <c r="EU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,22 +3734,22 @@
         <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0</v>
+        <v>-0.2235608930172721</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0</v>
+        <v>-0.09214297115267681</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>0.1289918045275673</v>
       </c>
       <c r="FD6" t="n">
         <v>0</v>
@@ -3758,25 +3758,25 @@
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0</v>
+        <v>-0.2746535673323783</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0</v>
+        <v>0.1099952914089675</v>
       </c>
       <c r="FL6" t="n">
-        <v>0</v>
+        <v>0.2169472446640782</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3788,58 +3788,5179 @@
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0</v>
+        <v>0.02145030635453575</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0</v>
+        <v>-0.001610381894443732</v>
       </c>
       <c r="FU6" t="n">
-        <v>0</v>
+        <v>0.06508311184352066</v>
       </c>
       <c r="FV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
         <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0</v>
+        <v>-0.06525846861944025</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>0</v>
+        <v>0.0849664408478213</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.3299765249468219</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1123264714252058</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.1103789159275546</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2964679144533628</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.2160316899098592</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.1913337115125338</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.07807913619732539</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>-0.09646662363721691</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.0656256725997347</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.04326384223121878</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>-0.08598000678252152</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.1862068770424346</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1829869378568756</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.05424731558797165</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.04319874496915061</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.3641672812815311</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0.008513409603161368</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.2322662064978384</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.01128692571034299</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0.08712315880478544</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.1562720255883576</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.02340393385583681</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-0.01078945224072814</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.07585564567903573</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.2081992352656575</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>-0.08020577042340028</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.02675693893681251</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.1126834825056884</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.06234537300221946</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.03695461836877327</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0.06987390676690518</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0.1794684173962625</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.1205331012697784</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.1017952815584377</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0.0714332092438341</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.04568831949854753</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.06166968328883793</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>-0.006797321696554705</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0.02033300467663687</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0.1020297616117637</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>-0.008288272583825976</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0.04174981834957928</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.005055227200589614</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0.05253592599456086</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0.07971624735265989</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0.03989310027746062</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0.03279379023633018</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0.009579882722175657</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0.03461125261203844</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>-0.0379352011909689</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0.0446432048831569</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0.1242214624567939</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0.06836526885864347</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.01702927222896753</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0.1242180204887785</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0.08841092758113765</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.1357526622994816</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.002373875100712118</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0.1575339894532056</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0.0176305647978272</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>-0.08298737852905015</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0.004374421809104102</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.7857662548049518</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.04794914669126656</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.4077274253834403</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8947255737677738</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.2831074735850482</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.1601389406243481</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.2757566359752214</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.09530914223506684</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.02557444985801751</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.08143552385535695</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.4423871473869151</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.05656052780862813</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.2951048149298868</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.01461370738131542</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.156270932531208</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.166197809885906</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.304508641099555</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.3404130113398762</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>-0.1539532946578639</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.3073784347282728</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.1445207434977043</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.09341370797058841</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.1610060010422677</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.1554571689042566</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.6628628311933195</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.01256659063797252</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.07266620307793981</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.297355825145163</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.02630020775122337</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.1823191479009334</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.3638254902297995</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.3703390814610866</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.01474157465988664</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.2747515663539845</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.03590111753043412</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.1939338218376665</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.2851167285224558</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.2183111715038567</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.1797065379078014</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.1884869593909214</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.05185470370434091</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.08506008356652996</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.003520347879352078</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>-0.1108018457059161</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.0108859142552588</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.1420643118743976</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.03452217563935239</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.03976308288622286</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.1986189464686053</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.2909968050402284</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>-0.3195820160881067</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.3403067953785645</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.01948406908923323</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.1800257370798246</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.2640552853389069</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.1846167101653065</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.1557193807208038</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.05240113943097616</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.02690447590669816</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.03236871433830496</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.1639008604184366</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.06451859214655818</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.4623958594137079</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2059397400011142</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2193397550876529</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.4639929713209044</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3628065741100486</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3136293209928301</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.04129973754596247</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.09171489792684762</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01477442814280253</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.07063442217935464</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.05522813590862802</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.03191389966766176</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>-0.2863388582337134</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.05805496797117912</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-0.240121974011436</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>-0.2383119030221186</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.1022622180250733</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.2084943526240589</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.004274273000112596</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.1003637005946716</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.202910383419675</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.109725318927826</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.04534939930964405</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.04793324383218996</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>-0.3764701704445628</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.1387439932159726</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.03416145821609481</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.2675583112890824</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-0.08006672865751885</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.01276169702253053</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.1465257235526451</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0.1792409831765951</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>-0.04722764515190528</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.2613267725792933</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>-0.07747300263705953</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.0216027005182498</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.1859471649292021</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-0.05311602635156848</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.04286336766486758</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.1435091096749778</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>-0.07887282132355689</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.004962860841333413</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.05832204724665864</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0.135650373894688</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.2550472973904284</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.2080155357190386</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>-0.0176263597931254</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.01440443926776544</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.1968265158281376</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0.02125575784277259</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.08374591133082206</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.2983293621846795</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>-0.1021515296291673</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.003905473716061712</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.1506267335227341</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>-0.05182895913321595</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.11893227367158</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>-0.1143839947755384</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>-0.202689255911345</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.04150020941377987</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.1509866661683807</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>-0.03753942878973242</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.3734371919531717</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.05604980942782805</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1874012635472954</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.4371883940492538</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.07037039221414509</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.1992972722732928</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.08486568555757919</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.008346401134848757</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.01047072870082801</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.02032261987634721</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.07816691703661222</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.0295711471403307</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.06767496361270733</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.04671732416132364</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.04551678130863552</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.3738466795150737</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.1480457485148621</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.08474435228054715</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.04236177213277641</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.007454956819045252</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.07932195952408089</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.03961802826434687</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.07661058189340955</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.03773051590411389</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.2128528845010788</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.008280092139729531</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.07798845497666576</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1199332086896117</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.001144892750590707</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.07347333849158802</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.03406625716382029</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.06886471196527989</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.03119728660709225</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1145390261190242</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.0102451577781615</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.08983939854241807</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.02578393001461353</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.06417721689749942</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.03272943641925012</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.009130062946403132</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.07740642978467928</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>-0.07962402654613267</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>-0.08682676126012347</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.009180403164633089</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.01709282785659263</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.05442763061136732</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.04771414665137119</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.03752199721963589</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.02426872415457105</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.01771984855561505</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.001852603174820047</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.1280201208771183</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.03208956021537349</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.06533721245543839</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.1192652518933075</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.001165171202975594</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.1083430611080591</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.18926086242125</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>-0.01535190290521754</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.06216494843390912</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.03843669196570932</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.02186353920059785</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.4189348712167296</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1292272330738801</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0191643217558568</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.4601758083253589</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2736126993482758</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.09841835085419208</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.09173092023724989</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.01926489560304549</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.04562586162809935</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.04534214674592658</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1682487485288402</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.1974406653462206</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1888655299255638</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.009679267540599669</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.2463179234430553</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.2647228386145157</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.1418362817023444</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.001418492712748904</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.0415178088438313</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.0344471256152601</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.1538389943601906</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1393501568211614</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.1102711475446346</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.05334509482592359</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.2353413636161004</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.09492272560488328</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.04300320924595175</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.2247438025601735</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0.05477432725783085</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.03612044911133495</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.08159552303664322</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0.2050609675494428</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.07722937550090865</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.2294371553989194</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0.06846844343554144</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.006527582812491457</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.03716467572643836</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0.04079071451236024</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.0367276147518728</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.1427072424768442</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0.0173718428038943</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.03464872197099499</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.002840100527013716</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.0623948774777105</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.04669102042169255</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.2502964581277528</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0.07564905221592839</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.01166883012850973</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.1669099376867705</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0.01957543060933035</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>-0.02638790079770442</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.2634929638301925</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0.07938558406268102</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.04250462708370811</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.08394980954978057</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.1287161401503443</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.1163035488809731</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.2620005422984603</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.04713265097325894</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.06335062132692834</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.2198904243029994</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0.01909602163398952</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3589366156143811</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.1413670612073765</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.1588386314531318</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.4470623858280252</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.2729995432342168</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.1916423893895911</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.1126291833975379</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1287019447708709</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.02528480775396432</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.05120866673450421</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.2412647071999132</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.07795283935662552</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.01868691085987982</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.0763807359653207</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.02257422901351181</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.4629446459062332</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.329701588922749</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.1737767027238781</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.05001868749950392</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.02079684530505826</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.01379770212377426</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.07948446041447785</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.1011407380793967</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.01352821196086084</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.2515643134050074</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.122185798410668</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.07969053628510719</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.09587887677954478</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.0755925283802908</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.04945025919364043</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.1324776507104911</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.1973461194695726</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.0776201648812886</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1005033585883444</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.06645049591478827</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.0725059363976263</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.03664847883237508</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1463594703313993</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.02360695907737883</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.01081415484083633</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>-0.07773908032152567</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.04601238611794111</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.001190332033190478</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.004396118371658954</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.01252824357680904</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.0495169492888145</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.06232939408517008</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.007286963896077719</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.00702234032950216</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.02320197369797464</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.1002155167406731</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1152526299378618</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.05287249718681277</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.0398577628428312</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1959258416842777</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.110762871078882</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1029680243376496</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0.08983042307953243</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>-0.1649008288540149</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.06344980953019323</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.05495855541205839</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.1005367365520448</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.4062987902693125</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.667947769946711</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.1668158471494346</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.3450088643579661</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.7850967315157229</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.381856463405932</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.05044839628068259</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>-0.08934656660526932</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.2361829521557334</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.05173935330378485</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>-0.1114270056687545</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.07454434720164488</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.2081759246062258</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-0.2331606476922457</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.07665629410211407</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.3396569560138033</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>-0.4297721499290578</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.6362340875299248</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.02649915072942462</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>-0.0925019724282741</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.2208879312940973</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.1608592679504047</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0.2797174849433111</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.06927848241739615</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.1905876701633716</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>-0.3468932606305711</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.233802814334694</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.08002947027803183</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.3565410112699491</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.06067817778732149</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.03103535027323063</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0.3993825896680289</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.098952928303718</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.06318670359827935</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0.3776783594794212</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.09713500505242412</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.0893953737175157</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>-0.03846916515908202</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.08118174248581235</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.1413252060525848</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0.0645818629669638</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0.05146349949605173</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.06558425082499082</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0.2203391334684893</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.06264866050248914</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.004236567862427338</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0.2902282680337786</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.06244176070029024</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.06135124757000782</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0.2763064528869266</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.009818906222062367</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.09416855586892568</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0.4159319289365426</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.04958552064126728</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.07358209368207204</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0.2405166339686465</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.03909890747064543</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.03308460405790351</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0.3461665657879425</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>-0.1420226767469132</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0.1033504383484878</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0.2451318208346473</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
